--- a/KeywordDrivenFramework/src/test/resources/ExcelFile/BillingAdd.xlsx
+++ b/KeywordDrivenFramework/src/test/resources/ExcelFile/BillingAdd.xlsx
@@ -24,40 +24,51 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
-  <si>
-    <t>Country</t>
-  </si>
-  <si>
-    <t>City</t>
-  </si>
-  <si>
-    <t>Address</t>
-  </si>
-  <si>
-    <t>PinCode</t>
-  </si>
-  <si>
-    <t>PhNo</t>
-  </si>
-  <si>
-    <t>India</t>
-  </si>
-  <si>
-    <t>Pune</t>
-  </si>
-  <si>
-    <t>Warje Jakat naka</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="9">
+  <si>
+    <t>First Name</t>
+  </si>
+  <si>
+    <t>Last Name</t>
+  </si>
+  <si>
+    <t>Email</t>
+  </si>
+  <si>
+    <t>Passward</t>
+  </si>
+  <si>
+    <t>ConfirmPassward</t>
+  </si>
+  <si>
+    <t>Rasika</t>
+  </si>
+  <si>
+    <t>Kahane</t>
+  </si>
+  <si>
+    <t>admin@123</t>
+  </si>
+  <si>
+    <t>rasikaK1201@gmail.com</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -80,13 +91,16 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -368,8 +382,13 @@
   <dimension ref="A1:E2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="15.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.5703125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.85546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -396,17 +415,22 @@
       <c r="B2" t="s">
         <v>6</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D2">
-        <v>4110058</v>
-      </c>
-      <c r="E2">
-        <v>9988776650</v>
+      <c r="E2" s="1" t="s">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="C2" r:id="rId1"/>
+    <hyperlink ref="D2" r:id="rId2"/>
+    <hyperlink ref="E2" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>